--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128232060</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,6 +775,536 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133853339</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58502</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vintervägstjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>786386</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7129927</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133853466</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vintervägstjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>786290</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7129843</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133853469</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vintervägstjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>786310</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7129851</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133853506</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58090</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vintervägstjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>786322</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7129865</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133853250</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vintervägstjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>786320</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7129976</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133853339</v>
       </c>
       <c r="B3" t="n">
-        <v>58502</v>
+        <v>58509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>133853466</v>
       </c>
       <c r="B4" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>133853469</v>
       </c>
       <c r="B5" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>133853506</v>
       </c>
       <c r="B6" t="n">
-        <v>58090</v>
+        <v>58097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>133853250</v>
       </c>
       <c r="B7" t="n">
-        <v>58393</v>
+        <v>58400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133853339</v>
       </c>
       <c r="B3" t="n">
-        <v>58509</v>
+        <v>58519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>133853466</v>
       </c>
       <c r="B4" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>133853469</v>
       </c>
       <c r="B5" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>133853506</v>
       </c>
       <c r="B6" t="n">
-        <v>58097</v>
+        <v>58107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>133853250</v>
       </c>
       <c r="B7" t="n">
-        <v>58400</v>
+        <v>58410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2025 artfynd.xlsx
+++ b/artfynd/A 24114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853339</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853466</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133853506</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,8 +1334,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128232060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>